--- a/data/trans_bre/P44-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P44-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,8</t>
+          <t>-3,86; 1,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,72</t>
+          <t>-5,3; 0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,24; -3,87</t>
+          <t>-13,46; -4,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,07; 30,87</t>
+          <t>-39,98; 27,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 9,56</t>
+          <t>-44,72; 11,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -12,08</t>
+          <t>-34,48; -12,29</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,35</t>
+          <t>-7,8; 1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -2,71</t>
+          <t>-9,11; -2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -4,94</t>
+          <t>-52,9; -6,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 18,57</t>
+          <t>-58,18; 12,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,09; -26,74</t>
+          <t>-68,33; -27,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,36; -20,1</t>
+          <t>-76,96; -27,96</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 18,76</t>
+          <t>-7,75; 18,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 6,01</t>
+          <t>-13,78; 4,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 2,93</t>
+          <t>-13,21; 2,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 189,83</t>
+          <t>-42,71; 203,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 50,96</t>
+          <t>-61,73; 40,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 7,47</t>
+          <t>-26,82; 5,65</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,25</t>
+          <t>-4,41; 0,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -2,09</t>
+          <t>-6,49; -2,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -7,31</t>
+          <t>-41,8; -7,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 3,01</t>
+          <t>-40,47; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,33; -20,7</t>
+          <t>-50,28; -19,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,92; -20,48</t>
+          <t>-66,55; -20,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P44-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P44-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,65</t>
+          <t>-7,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-24,5%</t>
+          <t>-21,99%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,52</t>
+          <t>-3,57; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,94</t>
+          <t>-5,18; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -4,15</t>
+          <t>-12,27; -2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 27,42</t>
+          <t>-39,06; 30,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 11,61</t>
+          <t>-44,47; 11,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,48; -12,29</t>
+          <t>-32,28; -9,49</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,23</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-52,51%</t>
+          <t>-10,76%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 1,23</t>
+          <t>-8,3; 0,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -2,61</t>
+          <t>-9,37; -3,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,9; -6,57</t>
+          <t>-7,89; -0,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 12,91</t>
+          <t>-58,58; 8,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,33; -27,3</t>
+          <t>-67,73; -28,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,96; -27,96</t>
+          <t>-21,7; -0,02</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-4,79</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,19%</t>
+          <t>-10,89%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 18,64</t>
+          <t>-7,74; 17,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 4,97</t>
+          <t>-14,33; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 2,14</t>
+          <t>-11,87; 2,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 203,23</t>
+          <t>-44,19; 200,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 40,5</t>
+          <t>-63,56; 39,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 5,65</t>
+          <t>-25,45; 6,88</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-19,02</t>
+          <t>-5,74</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-41,67%</t>
+          <t>-15,9%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,13</t>
+          <t>-4,46; 0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -2,05</t>
+          <t>-6,61; -2,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -7,6</t>
+          <t>-8,55; -3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 1,72</t>
+          <t>-41,55; 0,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,28; -19,96</t>
+          <t>-50,61; -20,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,55; -20,82</t>
+          <t>-22,74; -8,98</t>
         </is>
       </c>
     </row>
